--- a/backend/public/templates/template_file.xlsx
+++ b/backend/public/templates/template_file.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Request Template" sheetId="1" state="visible" r:id="rId3"/>
@@ -1183,7 +1183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="288">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1549,7 +1549,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="15" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1680,228 +1688,228 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2411,9 +2419,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1645920</xdr:colOff>
+      <xdr:colOff>1645560</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>169200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2427,7 +2435,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1857240" cy="664920"/>
+          <a:ext cx="1856880" cy="664560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2454,9 +2462,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1579320</xdr:colOff>
+      <xdr:colOff>1578960</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>157680</xdr:rowOff>
+      <xdr:rowOff>157320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2470,7 +2478,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1861200" cy="664920"/>
+          <a:ext cx="1860840" cy="664560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2497,9 +2505,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>968040</xdr:colOff>
+      <xdr:colOff>967680</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2513,7 +2521,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1360440" cy="483840"/>
+          <a:ext cx="1360080" cy="483480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2540,9 +2548,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1388520</xdr:colOff>
+      <xdr:colOff>1388160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
+      <xdr:rowOff>35640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2556,7 +2564,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1952280" cy="506520"/>
+          <a:ext cx="1951920" cy="506160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3650,45 +3658,45 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
     </row>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="93" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
       <c r="J3" s="37" t="s">
         <v>59</v>
       </c>
@@ -3696,7 +3704,7 @@
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="92"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="1"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
@@ -3705,30 +3713,30 @@
       <c r="I4" s="18"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" s="93" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" s="95" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="30" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="39"/>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="96"/>
-      <c r="L5" s="97"/>
-    </row>
-    <row r="6" s="101" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="98" t="s">
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="98"/>
+      <c r="L5" s="99"/>
+    </row>
+    <row r="6" s="103" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="102" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="47" t="s">
@@ -3749,288 +3757,288 @@
       <c r="I6" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="J6" s="98" t="s">
+      <c r="J6" s="100" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="106"/>
-    </row>
-    <row r="8" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="105"/>
-      <c r="I8" s="105"/>
-      <c r="J8" s="105"/>
-      <c r="K8" s="108"/>
-    </row>
-    <row r="9" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="102"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="108"/>
-    </row>
-    <row r="10" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="102"/>
-      <c r="B10" s="103"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="105"/>
-      <c r="J10" s="105"/>
-      <c r="K10" s="108"/>
-    </row>
-    <row r="11" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="102"/>
-      <c r="B11" s="103"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="105"/>
-      <c r="J11" s="105"/>
-      <c r="K11" s="108"/>
-    </row>
-    <row r="12" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="102"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="108"/>
-    </row>
-    <row r="13" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="102"/>
-      <c r="B13" s="103"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="108"/>
-    </row>
-    <row r="14" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="102"/>
-      <c r="B14" s="103"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="105"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="108"/>
-      <c r="M14" s="109"/>
-    </row>
-    <row r="15" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="102"/>
-      <c r="B15" s="103"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="105"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="108"/>
-    </row>
-    <row r="16" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="105"/>
-      <c r="J16" s="105"/>
-      <c r="K16" s="108"/>
-    </row>
-    <row r="17" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="108"/>
-    </row>
-    <row r="18" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="108"/>
-      <c r="M18" s="110"/>
-    </row>
-    <row r="19" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="108"/>
-      <c r="M19" s="110"/>
-    </row>
-    <row r="20" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="108"/>
-      <c r="M20" s="110"/>
-    </row>
-    <row r="21" s="107" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="108"/>
-      <c r="M21" s="110"/>
-    </row>
-    <row r="22" s="101" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="111" t="s">
+    <row r="7" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="108"/>
+    </row>
+    <row r="8" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="104"/>
+      <c r="B8" s="105"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
+      <c r="K8" s="110"/>
+    </row>
+    <row r="9" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="104"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="110"/>
+    </row>
+    <row r="10" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="104"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="106"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="110"/>
+    </row>
+    <row r="11" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="104"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="110"/>
+    </row>
+    <row r="12" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="104"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="110"/>
+    </row>
+    <row r="13" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="110"/>
+    </row>
+    <row r="14" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="106"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="107"/>
+      <c r="I14" s="107"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="110"/>
+      <c r="M14" s="111"/>
+    </row>
+    <row r="15" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="110"/>
+    </row>
+    <row r="16" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="106"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="107"/>
+      <c r="I16" s="107"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="110"/>
+    </row>
+    <row r="17" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="104"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="106"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="110"/>
+    </row>
+    <row r="18" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="104"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="107"/>
+      <c r="J18" s="107"/>
+      <c r="K18" s="110"/>
+      <c r="M18" s="112"/>
+    </row>
+    <row r="19" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="104"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="107"/>
+      <c r="H19" s="107"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="107"/>
+      <c r="K19" s="110"/>
+      <c r="M19" s="112"/>
+    </row>
+    <row r="20" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="104"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="107"/>
+      <c r="J20" s="107"/>
+      <c r="K20" s="110"/>
+      <c r="M20" s="112"/>
+    </row>
+    <row r="21" s="109" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="110"/>
+      <c r="M21" s="112"/>
+    </row>
+    <row r="22" s="103" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="113"/>
       <c r="E22" s="45"/>
       <c r="F22" s="75"/>
-      <c r="G22" s="112" t="n">
+      <c r="G22" s="114" t="n">
         <f aca="false">SUM(G7:G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="112" t="n">
+      <c r="H22" s="114" t="n">
         <f aca="false">SUM(H7:H21)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="112" t="n">
+      <c r="I22" s="114" t="n">
         <f aca="false">SUM(I7:I21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="113"/>
-      <c r="K22" s="114"/>
-    </row>
-    <row r="23" s="101" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J22" s="115"/>
+      <c r="K22" s="116"/>
+    </row>
+    <row r="23" s="103" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="33"/>
-      <c r="B23" s="115"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="117"/>
+      <c r="B23" s="117"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
       <c r="E23" s="33"/>
       <c r="F23" s="33"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
       <c r="I23" s="33"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="114"/>
-    </row>
-    <row r="24" s="101" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J23" s="119"/>
+      <c r="K23" s="116"/>
+    </row>
+    <row r="24" s="103" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
         <v>69</v>
       </c>
       <c r="B24" s="45"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="100"/>
+      <c r="E24" s="100"/>
       <c r="F24" s="33"/>
       <c r="G24" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="H24" s="119"/>
-      <c r="I24" s="119"/>
-      <c r="J24" s="119"/>
-      <c r="K24" s="114"/>
-    </row>
-    <row r="25" s="120" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H24" s="121"/>
+      <c r="I24" s="121"/>
+      <c r="J24" s="121"/>
+      <c r="K24" s="116"/>
+    </row>
+    <row r="25" s="122" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="45" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
       <c r="F25" s="33"/>
     </row>
-    <row r="26" s="120" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="121"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="116"/>
+    <row r="26" s="122" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="123"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="118"/>
       <c r="D26" s="90"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="121"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="123"/>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
       <c r="J26" s="33"/>
-      <c r="K26" s="123"/>
-    </row>
-    <row r="27" s="120" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="125"/>
+    </row>
+    <row r="27" s="122" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="84" t="s">
         <v>53</v>
       </c>
@@ -4039,20 +4047,20 @@
         <v>54</v>
       </c>
       <c r="D27" s="55"/>
-      <c r="E27" s="67" t="s">
+      <c r="E27" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="124"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
       <c r="I27" s="84" t="s">
         <v>56</v>
       </c>
       <c r="J27" s="84"/>
-      <c r="K27" s="123"/>
-      <c r="M27" s="125"/>
-    </row>
-    <row r="28" s="120" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K27" s="125"/>
+      <c r="M27" s="126"/>
+    </row>
+    <row r="28" s="122" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="84"/>
       <c r="B28" s="84"/>
       <c r="C28" s="84"/>
@@ -4063,7 +4071,7 @@
       <c r="H28" s="84"/>
       <c r="I28" s="84"/>
       <c r="J28" s="84"/>
-      <c r="K28" s="123"/>
+      <c r="K28" s="125"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="84"/>
@@ -4076,7 +4084,7 @@
       <c r="H29" s="84"/>
       <c r="I29" s="84"/>
       <c r="J29" s="84"/>
-      <c r="L29" s="126"/>
+      <c r="L29" s="127"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="84" t="s">
@@ -4099,7 +4107,7 @@
       <c r="J30" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:I3"/>
@@ -4111,6 +4119,7 @@
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:H27"/>
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
@@ -4144,860 +4153,860 @@
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="11.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="127" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="127" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="127" width="7.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="127" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="127" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="127" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="127" width="8.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="127" width="7.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="127" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="127" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="127" width="8.42"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="127" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="128" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="128" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="128" width="7.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="128" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="128" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="128" width="7.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="128" width="8.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="128" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="128" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="128" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="128" width="8.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="128" width="9.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="128"/>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="131" t="s">
+      <c r="A1" s="129"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="132" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="132"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="134" t="s">
+      <c r="A2" s="133"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="135"/>
-      <c r="F3" s="136" t="s">
+      <c r="A3" s="136"/>
+      <c r="F3" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="137"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="139"/>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="132" t="s">
+      <c r="A4" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="139" t="s">
+      <c r="I4" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="140"/>
-      <c r="K4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="142"/>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="143" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="145" t="s">
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="146" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="143"/>
-      <c r="K5" s="141"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="143" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="143"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="143"/>
-      <c r="E6" s="143"/>
-      <c r="F6" s="146"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="145" t="s">
+      <c r="B6" s="144"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="147"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="143"/>
-      <c r="K6" s="141"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="142"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="143"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="143"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="143"/>
-      <c r="I7" s="144"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="147"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="145"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="148"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="142" t="s">
+      <c r="A8" s="143" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="143"/>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
-      <c r="E8" s="143"/>
-      <c r="F8" s="143"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="144"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="147"/>
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="144"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="145"/>
+      <c r="K8" s="148"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="142" t="s">
+      <c r="A9" s="143" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="143"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="143"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="143"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144"/>
-      <c r="K9" s="147"/>
+      <c r="B9" s="144"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="144"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="145"/>
+      <c r="K9" s="148"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="142" t="s">
+      <c r="A10" s="143" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
-      <c r="E10" s="143"/>
-      <c r="F10" s="143"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="143"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="144"/>
-      <c r="K10" s="147"/>
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="145"/>
+      <c r="K10" s="148"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="149" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="148"/>
-      <c r="C11" s="149" t="s">
+      <c r="B11" s="149"/>
+      <c r="C11" s="150" t="s">
         <v>85</v>
       </c>
-      <c r="D11" s="150"/>
-      <c r="E11" s="149" t="s">
+      <c r="D11" s="151"/>
+      <c r="E11" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="149" t="s">
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="150"/>
-      <c r="J11" s="149" t="s">
+      <c r="I11" s="151"/>
+      <c r="J11" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="K11" s="151"/>
+      <c r="K11" s="152"/>
     </row>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="152"/>
-      <c r="B12" s="153"/>
-      <c r="C12" s="154" t="s">
+      <c r="A12" s="153"/>
+      <c r="B12" s="154"/>
+      <c r="C12" s="155" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="153"/>
-      <c r="E12" s="154" t="s">
+      <c r="D12" s="154"/>
+      <c r="E12" s="155" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="154"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="155" t="s">
+      <c r="F12" s="155"/>
+      <c r="G12" s="154"/>
+      <c r="H12" s="156" t="s">
         <v>90</v>
       </c>
-      <c r="I12" s="153"/>
-      <c r="J12" s="152" t="s">
+      <c r="I12" s="154"/>
+      <c r="J12" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="156"/>
+      <c r="K12" s="157"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="157" t="s">
+      <c r="A13" s="158" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="158"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="159"/>
-      <c r="I13" s="158"/>
-      <c r="J13" s="157"/>
-      <c r="K13" s="160"/>
+      <c r="B13" s="159"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="159"/>
+      <c r="J13" s="158"/>
+      <c r="K13" s="161"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="158" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="158"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="158"/>
-      <c r="J14" s="157"/>
-      <c r="K14" s="158"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="158"/>
+      <c r="K14" s="159"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="158" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="158"/>
-      <c r="C15" s="137"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="158"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="158"/>
-      <c r="J15" s="157"/>
-      <c r="K15" s="158"/>
+      <c r="B15" s="159"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="159"/>
+      <c r="H15" s="138"/>
+      <c r="I15" s="159"/>
+      <c r="J15" s="158"/>
+      <c r="K15" s="159"/>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="161" t="s">
+      <c r="A16" s="162" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="162"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="163"/>
-      <c r="F16" s="163"/>
-      <c r="G16" s="162"/>
-      <c r="H16" s="163"/>
-      <c r="I16" s="162"/>
-      <c r="J16" s="161"/>
-      <c r="K16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="163"/>
+      <c r="E16" s="164"/>
+      <c r="F16" s="164"/>
+      <c r="G16" s="163"/>
+      <c r="H16" s="164"/>
+      <c r="I16" s="163"/>
+      <c r="J16" s="162"/>
+      <c r="K16" s="163"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="164" t="s">
+      <c r="A17" s="165" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="164"/>
-      <c r="C17" s="164"/>
-      <c r="D17" s="164"/>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="164"/>
-      <c r="I17" s="164"/>
-      <c r="J17" s="164"/>
-      <c r="K17" s="164"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="165"/>
+      <c r="E17" s="165"/>
+      <c r="F17" s="165"/>
+      <c r="G17" s="165"/>
+      <c r="H17" s="165"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="165"/>
+      <c r="K17" s="165"/>
     </row>
     <row r="18" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="165" t="s">
+      <c r="A18" s="166" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="165"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="165" t="s">
+      <c r="B18" s="166"/>
+      <c r="C18" s="166"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="165"/>
-      <c r="G18" s="165"/>
-      <c r="H18" s="166" t="s">
+      <c r="F18" s="166"/>
+      <c r="G18" s="166"/>
+      <c r="H18" s="167" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="166" t="s">
+      <c r="I18" s="167" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="166" t="s">
+      <c r="J18" s="167" t="s">
         <v>100</v>
       </c>
-      <c r="K18" s="165" t="s">
+      <c r="K18" s="166" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="165" t="s">
+      <c r="A19" s="166" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="165" t="s">
+      <c r="B19" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="165" t="s">
+      <c r="C19" s="166" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="165" t="s">
+      <c r="D19" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="165" t="s">
+      <c r="E19" s="166" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="165" t="s">
+      <c r="F19" s="166" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="166" t="s">
+      <c r="G19" s="167" t="s">
         <v>104</v>
       </c>
-      <c r="H19" s="166"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="165"/>
+      <c r="H19" s="167"/>
+      <c r="I19" s="167"/>
+      <c r="J19" s="167"/>
+      <c r="K19" s="166"/>
     </row>
     <row r="20" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="165"/>
-      <c r="B20" s="167"/>
-      <c r="C20" s="167"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="168"/>
-      <c r="H20" s="168"/>
-      <c r="I20" s="167"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="167"/>
+      <c r="A20" s="166"/>
+      <c r="B20" s="168"/>
+      <c r="C20" s="168"/>
+      <c r="D20" s="168"/>
+      <c r="E20" s="169"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="169"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="168"/>
+      <c r="J20" s="170"/>
+      <c r="K20" s="168"/>
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="165"/>
-      <c r="B21" s="167"/>
-      <c r="C21" s="167"/>
-      <c r="D21" s="167"/>
-      <c r="E21" s="168"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="168"/>
-      <c r="H21" s="168"/>
-      <c r="I21" s="167"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="170"/>
+      <c r="A21" s="166"/>
+      <c r="B21" s="168"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="168"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="169"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="168"/>
+      <c r="J21" s="170"/>
+      <c r="K21" s="171"/>
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="165"/>
-      <c r="B22" s="167"/>
-      <c r="C22" s="167"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="168"/>
-      <c r="H22" s="168"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="167"/>
+      <c r="A22" s="166"/>
+      <c r="B22" s="168"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="168"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="169"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="168"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="168"/>
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="165"/>
-      <c r="B23" s="167"/>
-      <c r="C23" s="167"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="168"/>
-      <c r="H23" s="168"/>
-      <c r="I23" s="167"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="167"/>
+      <c r="A23" s="166"/>
+      <c r="B23" s="168"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="168"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="169"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="168"/>
+      <c r="J23" s="170"/>
+      <c r="K23" s="168"/>
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="165"/>
-      <c r="B24" s="167"/>
-      <c r="C24" s="167"/>
-      <c r="D24" s="167"/>
-      <c r="E24" s="168"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="168"/>
-      <c r="H24" s="168"/>
-      <c r="I24" s="167"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="167"/>
+      <c r="A24" s="166"/>
+      <c r="B24" s="168"/>
+      <c r="C24" s="168"/>
+      <c r="D24" s="168"/>
+      <c r="E24" s="169"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="169"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="168"/>
+      <c r="J24" s="170"/>
+      <c r="K24" s="168"/>
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="165"/>
-      <c r="B25" s="167"/>
-      <c r="C25" s="167"/>
-      <c r="D25" s="167"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="168"/>
-      <c r="H25" s="168"/>
-      <c r="I25" s="167"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="167"/>
+      <c r="A25" s="166"/>
+      <c r="B25" s="168"/>
+      <c r="C25" s="168"/>
+      <c r="D25" s="168"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="168"/>
+      <c r="J25" s="170"/>
+      <c r="K25" s="168"/>
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="165"/>
-      <c r="B26" s="167"/>
-      <c r="C26" s="167"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="168"/>
-      <c r="I26" s="167"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="167"/>
+      <c r="A26" s="166"/>
+      <c r="B26" s="168"/>
+      <c r="C26" s="168"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="169"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="168"/>
+      <c r="J26" s="170"/>
+      <c r="K26" s="168"/>
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="165"/>
-      <c r="B27" s="167"/>
-      <c r="C27" s="167"/>
-      <c r="D27" s="167"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="168"/>
-      <c r="H27" s="168"/>
-      <c r="I27" s="167"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="167"/>
+      <c r="A27" s="166"/>
+      <c r="B27" s="168"/>
+      <c r="C27" s="168"/>
+      <c r="D27" s="168"/>
+      <c r="E27" s="169"/>
+      <c r="F27" s="169"/>
+      <c r="G27" s="169"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="168"/>
+      <c r="J27" s="170"/>
+      <c r="K27" s="168"/>
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="165"/>
-      <c r="B28" s="167"/>
-      <c r="C28" s="167"/>
-      <c r="D28" s="167"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="168"/>
-      <c r="H28" s="168"/>
-      <c r="I28" s="167"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="167"/>
+      <c r="A28" s="166"/>
+      <c r="B28" s="168"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="168"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="169"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="168"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="168"/>
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="165"/>
-      <c r="B29" s="167"/>
-      <c r="C29" s="167"/>
-      <c r="D29" s="167"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="168"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="167"/>
-      <c r="J29" s="169"/>
-      <c r="K29" s="167"/>
+      <c r="A29" s="166"/>
+      <c r="B29" s="168"/>
+      <c r="C29" s="168"/>
+      <c r="D29" s="168"/>
+      <c r="E29" s="169"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="169"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="168"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="168"/>
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="165"/>
-      <c r="B30" s="167"/>
-      <c r="C30" s="167"/>
-      <c r="D30" s="167"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="168"/>
-      <c r="H30" s="168"/>
-      <c r="I30" s="167"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="167"/>
+      <c r="A30" s="166"/>
+      <c r="B30" s="168"/>
+      <c r="C30" s="168"/>
+      <c r="D30" s="168"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="168"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="168"/>
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="165"/>
-      <c r="B31" s="167"/>
-      <c r="C31" s="167"/>
-      <c r="D31" s="167"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="168"/>
-      <c r="H31" s="168"/>
-      <c r="I31" s="167"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="167"/>
+      <c r="A31" s="166"/>
+      <c r="B31" s="168"/>
+      <c r="C31" s="168"/>
+      <c r="D31" s="168"/>
+      <c r="E31" s="169"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="168"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="168"/>
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="165"/>
-      <c r="B32" s="167"/>
-      <c r="C32" s="167"/>
-      <c r="D32" s="167"/>
-      <c r="E32" s="168"/>
-      <c r="F32" s="168"/>
-      <c r="G32" s="168"/>
-      <c r="H32" s="168"/>
-      <c r="I32" s="167"/>
-      <c r="J32" s="169"/>
-      <c r="K32" s="167"/>
+      <c r="A32" s="166"/>
+      <c r="B32" s="168"/>
+      <c r="C32" s="168"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="169"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="168"/>
+      <c r="J32" s="170"/>
+      <c r="K32" s="168"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="165"/>
-      <c r="B33" s="167"/>
-      <c r="C33" s="167"/>
-      <c r="D33" s="167"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="168"/>
-      <c r="H33" s="168"/>
-      <c r="I33" s="167"/>
-      <c r="J33" s="169"/>
-      <c r="K33" s="167"/>
+      <c r="A33" s="166"/>
+      <c r="B33" s="168"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="169"/>
+      <c r="F33" s="169"/>
+      <c r="G33" s="169"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="168"/>
+      <c r="J33" s="170"/>
+      <c r="K33" s="168"/>
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="165"/>
-      <c r="B34" s="167"/>
-      <c r="C34" s="167"/>
-      <c r="D34" s="167"/>
-      <c r="E34" s="168"/>
-      <c r="F34" s="168"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="168"/>
-      <c r="I34" s="167"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="167"/>
+      <c r="A34" s="166"/>
+      <c r="B34" s="168"/>
+      <c r="C34" s="168"/>
+      <c r="D34" s="168"/>
+      <c r="E34" s="169"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="168"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="168"/>
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="165"/>
-      <c r="B35" s="167"/>
-      <c r="C35" s="167"/>
-      <c r="D35" s="167"/>
-      <c r="E35" s="168"/>
-      <c r="F35" s="168"/>
-      <c r="G35" s="168"/>
-      <c r="H35" s="168"/>
-      <c r="I35" s="167"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="167"/>
+      <c r="A35" s="166"/>
+      <c r="B35" s="168"/>
+      <c r="C35" s="168"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="169"/>
+      <c r="F35" s="169"/>
+      <c r="G35" s="169"/>
+      <c r="H35" s="169"/>
+      <c r="I35" s="168"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="168"/>
     </row>
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="165"/>
-      <c r="B36" s="167"/>
-      <c r="C36" s="167"/>
-      <c r="D36" s="167"/>
-      <c r="E36" s="168"/>
-      <c r="F36" s="168"/>
-      <c r="G36" s="168"/>
-      <c r="H36" s="168"/>
-      <c r="I36" s="167"/>
-      <c r="J36" s="169"/>
-      <c r="K36" s="167"/>
+      <c r="A36" s="166"/>
+      <c r="B36" s="168"/>
+      <c r="C36" s="168"/>
+      <c r="D36" s="168"/>
+      <c r="E36" s="169"/>
+      <c r="F36" s="169"/>
+      <c r="G36" s="169"/>
+      <c r="H36" s="169"/>
+      <c r="I36" s="168"/>
+      <c r="J36" s="170"/>
+      <c r="K36" s="168"/>
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="165"/>
-      <c r="B37" s="167"/>
-      <c r="C37" s="167"/>
-      <c r="D37" s="167"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="167"/>
-      <c r="J37" s="169"/>
-      <c r="K37" s="167"/>
+      <c r="A37" s="166"/>
+      <c r="B37" s="168"/>
+      <c r="C37" s="168"/>
+      <c r="D37" s="168"/>
+      <c r="E37" s="169"/>
+      <c r="F37" s="169"/>
+      <c r="G37" s="169"/>
+      <c r="H37" s="169"/>
+      <c r="I37" s="168"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="168"/>
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="165"/>
-      <c r="B38" s="167"/>
-      <c r="C38" s="167"/>
-      <c r="D38" s="167"/>
-      <c r="E38" s="168"/>
-      <c r="F38" s="168"/>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
-      <c r="I38" s="167"/>
-      <c r="J38" s="169"/>
-      <c r="K38" s="167"/>
+      <c r="A38" s="166"/>
+      <c r="B38" s="168"/>
+      <c r="C38" s="168"/>
+      <c r="D38" s="168"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="168"/>
+      <c r="J38" s="170"/>
+      <c r="K38" s="168"/>
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="165"/>
-      <c r="B39" s="167"/>
-      <c r="C39" s="167"/>
-      <c r="D39" s="167"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="167"/>
-      <c r="J39" s="169"/>
-      <c r="K39" s="167"/>
+      <c r="A39" s="166"/>
+      <c r="B39" s="168"/>
+      <c r="C39" s="168"/>
+      <c r="D39" s="168"/>
+      <c r="E39" s="169"/>
+      <c r="F39" s="169"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="169"/>
+      <c r="I39" s="168"/>
+      <c r="J39" s="170"/>
+      <c r="K39" s="168"/>
     </row>
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="165"/>
-      <c r="B40" s="167"/>
-      <c r="C40" s="167"/>
-      <c r="D40" s="167"/>
-      <c r="E40" s="168"/>
-      <c r="F40" s="168"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
-      <c r="I40" s="167"/>
-      <c r="J40" s="169"/>
-      <c r="K40" s="167"/>
+      <c r="A40" s="166"/>
+      <c r="B40" s="168"/>
+      <c r="C40" s="168"/>
+      <c r="D40" s="168"/>
+      <c r="E40" s="169"/>
+      <c r="F40" s="169"/>
+      <c r="G40" s="169"/>
+      <c r="H40" s="169"/>
+      <c r="I40" s="168"/>
+      <c r="J40" s="170"/>
+      <c r="K40" s="168"/>
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="165"/>
-      <c r="B41" s="167"/>
-      <c r="C41" s="167"/>
-      <c r="D41" s="167"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="168"/>
-      <c r="I41" s="167"/>
-      <c r="J41" s="169"/>
-      <c r="K41" s="167"/>
+      <c r="A41" s="166"/>
+      <c r="B41" s="168"/>
+      <c r="C41" s="168"/>
+      <c r="D41" s="168"/>
+      <c r="E41" s="169"/>
+      <c r="F41" s="169"/>
+      <c r="G41" s="169"/>
+      <c r="H41" s="169"/>
+      <c r="I41" s="168"/>
+      <c r="J41" s="170"/>
+      <c r="K41" s="168"/>
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="165"/>
-      <c r="B42" s="167"/>
-      <c r="C42" s="167"/>
-      <c r="D42" s="167"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="168"/>
-      <c r="H42" s="168"/>
-      <c r="I42" s="167"/>
-      <c r="J42" s="169"/>
-      <c r="K42" s="167"/>
+      <c r="A42" s="166"/>
+      <c r="B42" s="168"/>
+      <c r="C42" s="168"/>
+      <c r="D42" s="168"/>
+      <c r="E42" s="169"/>
+      <c r="F42" s="169"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="168"/>
+      <c r="J42" s="170"/>
+      <c r="K42" s="168"/>
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="165"/>
-      <c r="B43" s="167"/>
-      <c r="C43" s="167"/>
-      <c r="D43" s="167"/>
-      <c r="E43" s="168"/>
-      <c r="F43" s="168"/>
-      <c r="G43" s="168"/>
-      <c r="H43" s="168"/>
-      <c r="I43" s="167"/>
-      <c r="J43" s="169"/>
-      <c r="K43" s="167"/>
+      <c r="A43" s="166"/>
+      <c r="B43" s="168"/>
+      <c r="C43" s="168"/>
+      <c r="D43" s="168"/>
+      <c r="E43" s="169"/>
+      <c r="F43" s="169"/>
+      <c r="G43" s="169"/>
+      <c r="H43" s="169"/>
+      <c r="I43" s="168"/>
+      <c r="J43" s="170"/>
+      <c r="K43" s="168"/>
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="165"/>
-      <c r="B44" s="167"/>
-      <c r="C44" s="167"/>
-      <c r="D44" s="167"/>
-      <c r="E44" s="168"/>
-      <c r="F44" s="168"/>
-      <c r="G44" s="168"/>
-      <c r="H44" s="168"/>
-      <c r="I44" s="167"/>
-      <c r="J44" s="169"/>
-      <c r="K44" s="167"/>
+      <c r="A44" s="166"/>
+      <c r="B44" s="168"/>
+      <c r="C44" s="168"/>
+      <c r="D44" s="168"/>
+      <c r="E44" s="169"/>
+      <c r="F44" s="169"/>
+      <c r="G44" s="169"/>
+      <c r="H44" s="169"/>
+      <c r="I44" s="168"/>
+      <c r="J44" s="170"/>
+      <c r="K44" s="168"/>
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="165"/>
-      <c r="B45" s="167"/>
-      <c r="C45" s="167"/>
-      <c r="D45" s="167"/>
-      <c r="E45" s="168"/>
-      <c r="F45" s="168"/>
-      <c r="G45" s="168"/>
-      <c r="H45" s="168"/>
-      <c r="I45" s="167"/>
-      <c r="J45" s="169"/>
-      <c r="K45" s="167"/>
+      <c r="A45" s="166"/>
+      <c r="B45" s="168"/>
+      <c r="C45" s="168"/>
+      <c r="D45" s="168"/>
+      <c r="E45" s="169"/>
+      <c r="F45" s="169"/>
+      <c r="G45" s="169"/>
+      <c r="H45" s="169"/>
+      <c r="I45" s="168"/>
+      <c r="J45" s="170"/>
+      <c r="K45" s="168"/>
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="165"/>
-      <c r="B46" s="167"/>
-      <c r="C46" s="167"/>
-      <c r="D46" s="167"/>
-      <c r="E46" s="168"/>
-      <c r="F46" s="168"/>
-      <c r="G46" s="168"/>
-      <c r="H46" s="168"/>
-      <c r="I46" s="167"/>
-      <c r="J46" s="169"/>
-      <c r="K46" s="167"/>
+      <c r="A46" s="166"/>
+      <c r="B46" s="168"/>
+      <c r="C46" s="168"/>
+      <c r="D46" s="168"/>
+      <c r="E46" s="169"/>
+      <c r="F46" s="169"/>
+      <c r="G46" s="169"/>
+      <c r="H46" s="169"/>
+      <c r="I46" s="168"/>
+      <c r="J46" s="170"/>
+      <c r="K46" s="168"/>
     </row>
     <row r="47" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="165"/>
-      <c r="B47" s="167"/>
-      <c r="C47" s="167"/>
-      <c r="D47" s="167"/>
-      <c r="E47" s="168"/>
-      <c r="F47" s="168"/>
-      <c r="G47" s="168"/>
-      <c r="H47" s="168"/>
-      <c r="I47" s="167"/>
-      <c r="J47" s="169"/>
-      <c r="K47" s="167"/>
+      <c r="A47" s="166"/>
+      <c r="B47" s="168"/>
+      <c r="C47" s="168"/>
+      <c r="D47" s="168"/>
+      <c r="E47" s="169"/>
+      <c r="F47" s="169"/>
+      <c r="G47" s="169"/>
+      <c r="H47" s="169"/>
+      <c r="I47" s="168"/>
+      <c r="J47" s="170"/>
+      <c r="K47" s="168"/>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="165"/>
-      <c r="B48" s="167"/>
-      <c r="C48" s="167"/>
-      <c r="D48" s="167"/>
-      <c r="E48" s="168"/>
-      <c r="F48" s="168"/>
-      <c r="G48" s="168"/>
-      <c r="H48" s="168"/>
-      <c r="I48" s="167"/>
-      <c r="J48" s="169"/>
-      <c r="K48" s="167"/>
+      <c r="A48" s="166"/>
+      <c r="B48" s="168"/>
+      <c r="C48" s="168"/>
+      <c r="D48" s="168"/>
+      <c r="E48" s="169"/>
+      <c r="F48" s="169"/>
+      <c r="G48" s="169"/>
+      <c r="H48" s="169"/>
+      <c r="I48" s="168"/>
+      <c r="J48" s="170"/>
+      <c r="K48" s="168"/>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="165"/>
-      <c r="B49" s="167"/>
-      <c r="C49" s="167"/>
-      <c r="D49" s="167"/>
-      <c r="E49" s="168"/>
-      <c r="F49" s="168"/>
-      <c r="G49" s="168"/>
-      <c r="H49" s="168"/>
-      <c r="I49" s="167"/>
-      <c r="J49" s="169"/>
-      <c r="K49" s="167"/>
+      <c r="A49" s="166"/>
+      <c r="B49" s="168"/>
+      <c r="C49" s="168"/>
+      <c r="D49" s="168"/>
+      <c r="E49" s="169"/>
+      <c r="F49" s="169"/>
+      <c r="G49" s="169"/>
+      <c r="H49" s="169"/>
+      <c r="I49" s="168"/>
+      <c r="J49" s="170"/>
+      <c r="K49" s="168"/>
     </row>
     <row r="50" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="165"/>
-      <c r="B50" s="167"/>
-      <c r="C50" s="167"/>
-      <c r="D50" s="167"/>
-      <c r="E50" s="168"/>
-      <c r="F50" s="168"/>
-      <c r="G50" s="168"/>
-      <c r="H50" s="168"/>
-      <c r="I50" s="167"/>
-      <c r="J50" s="169"/>
-      <c r="K50" s="167"/>
+      <c r="A50" s="166"/>
+      <c r="B50" s="168"/>
+      <c r="C50" s="168"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="169"/>
+      <c r="F50" s="169"/>
+      <c r="G50" s="169"/>
+      <c r="H50" s="169"/>
+      <c r="I50" s="168"/>
+      <c r="J50" s="170"/>
+      <c r="K50" s="168"/>
     </row>
     <row r="51" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="165"/>
-      <c r="B51" s="167"/>
-      <c r="C51" s="167"/>
-      <c r="D51" s="167"/>
-      <c r="E51" s="168"/>
-      <c r="F51" s="168"/>
-      <c r="G51" s="168"/>
-      <c r="H51" s="168"/>
-      <c r="I51" s="167"/>
-      <c r="J51" s="169"/>
-      <c r="K51" s="167"/>
+      <c r="A51" s="166"/>
+      <c r="B51" s="168"/>
+      <c r="C51" s="168"/>
+      <c r="D51" s="168"/>
+      <c r="E51" s="169"/>
+      <c r="F51" s="169"/>
+      <c r="G51" s="169"/>
+      <c r="H51" s="169"/>
+      <c r="I51" s="168"/>
+      <c r="J51" s="170"/>
+      <c r="K51" s="168"/>
     </row>
     <row r="52" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="165"/>
-      <c r="B52" s="167"/>
-      <c r="C52" s="167"/>
-      <c r="D52" s="167"/>
-      <c r="E52" s="168"/>
-      <c r="F52" s="168"/>
-      <c r="G52" s="168"/>
-      <c r="H52" s="168"/>
-      <c r="I52" s="167"/>
-      <c r="J52" s="169"/>
-      <c r="K52" s="167"/>
+      <c r="A52" s="166"/>
+      <c r="B52" s="168"/>
+      <c r="C52" s="168"/>
+      <c r="D52" s="168"/>
+      <c r="E52" s="169"/>
+      <c r="F52" s="169"/>
+      <c r="G52" s="169"/>
+      <c r="H52" s="169"/>
+      <c r="I52" s="168"/>
+      <c r="J52" s="170"/>
+      <c r="K52" s="168"/>
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="165"/>
-      <c r="B53" s="167"/>
-      <c r="C53" s="167"/>
-      <c r="D53" s="167"/>
-      <c r="E53" s="168"/>
-      <c r="F53" s="168"/>
-      <c r="G53" s="168"/>
-      <c r="H53" s="168"/>
-      <c r="I53" s="167"/>
-      <c r="J53" s="169"/>
-      <c r="K53" s="167"/>
+      <c r="A53" s="166"/>
+      <c r="B53" s="168"/>
+      <c r="C53" s="168"/>
+      <c r="D53" s="168"/>
+      <c r="E53" s="169"/>
+      <c r="F53" s="169"/>
+      <c r="G53" s="169"/>
+      <c r="H53" s="169"/>
+      <c r="I53" s="168"/>
+      <c r="J53" s="170"/>
+      <c r="K53" s="168"/>
     </row>
     <row r="54" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="165"/>
-      <c r="B54" s="167"/>
-      <c r="C54" s="167"/>
-      <c r="D54" s="167"/>
-      <c r="E54" s="168"/>
-      <c r="F54" s="168"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="168"/>
-      <c r="I54" s="167"/>
-      <c r="J54" s="169"/>
-      <c r="K54" s="167"/>
+      <c r="A54" s="166"/>
+      <c r="B54" s="168"/>
+      <c r="C54" s="168"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="169"/>
+      <c r="F54" s="169"/>
+      <c r="G54" s="169"/>
+      <c r="H54" s="169"/>
+      <c r="I54" s="168"/>
+      <c r="J54" s="170"/>
+      <c r="K54" s="168"/>
     </row>
     <row r="55" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="165"/>
-      <c r="B55" s="167"/>
-      <c r="C55" s="167"/>
-      <c r="D55" s="167"/>
-      <c r="E55" s="168"/>
-      <c r="F55" s="168"/>
-      <c r="G55" s="168"/>
-      <c r="H55" s="168"/>
-      <c r="I55" s="167"/>
-      <c r="J55" s="169"/>
-      <c r="K55" s="167"/>
+      <c r="A55" s="166"/>
+      <c r="B55" s="168"/>
+      <c r="C55" s="168"/>
+      <c r="D55" s="168"/>
+      <c r="E55" s="169"/>
+      <c r="F55" s="169"/>
+      <c r="G55" s="169"/>
+      <c r="H55" s="169"/>
+      <c r="I55" s="168"/>
+      <c r="J55" s="170"/>
+      <c r="K55" s="168"/>
     </row>
     <row r="56" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="165"/>
-      <c r="B56" s="167"/>
-      <c r="C56" s="167"/>
-      <c r="D56" s="167"/>
-      <c r="E56" s="168"/>
-      <c r="F56" s="168"/>
-      <c r="G56" s="168"/>
-      <c r="H56" s="168"/>
-      <c r="I56" s="167"/>
-      <c r="J56" s="169"/>
-      <c r="K56" s="167"/>
+      <c r="A56" s="166"/>
+      <c r="B56" s="168"/>
+      <c r="C56" s="168"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="169"/>
+      <c r="F56" s="169"/>
+      <c r="G56" s="169"/>
+      <c r="H56" s="169"/>
+      <c r="I56" s="168"/>
+      <c r="J56" s="170"/>
+      <c r="K56" s="168"/>
     </row>
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="165"/>
-      <c r="B57" s="167"/>
-      <c r="C57" s="167"/>
-      <c r="D57" s="167"/>
-      <c r="E57" s="168"/>
-      <c r="F57" s="168"/>
-      <c r="G57" s="168"/>
-      <c r="H57" s="168"/>
-      <c r="I57" s="167"/>
-      <c r="J57" s="169"/>
-      <c r="K57" s="167"/>
+      <c r="A57" s="166"/>
+      <c r="B57" s="168"/>
+      <c r="C57" s="168"/>
+      <c r="D57" s="168"/>
+      <c r="E57" s="169"/>
+      <c r="F57" s="169"/>
+      <c r="G57" s="169"/>
+      <c r="H57" s="169"/>
+      <c r="I57" s="168"/>
+      <c r="J57" s="170"/>
+      <c r="K57" s="168"/>
     </row>
     <row r="58" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="165"/>
-      <c r="B58" s="167"/>
-      <c r="C58" s="167"/>
-      <c r="D58" s="167"/>
-      <c r="E58" s="168"/>
-      <c r="F58" s="168"/>
-      <c r="G58" s="168"/>
-      <c r="H58" s="168"/>
-      <c r="I58" s="167"/>
-      <c r="J58" s="169"/>
-      <c r="K58" s="167"/>
+      <c r="A58" s="166"/>
+      <c r="B58" s="168"/>
+      <c r="C58" s="168"/>
+      <c r="D58" s="168"/>
+      <c r="E58" s="169"/>
+      <c r="F58" s="169"/>
+      <c r="G58" s="169"/>
+      <c r="H58" s="169"/>
+      <c r="I58" s="168"/>
+      <c r="J58" s="170"/>
+      <c r="K58" s="168"/>
     </row>
     <row r="59" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="165"/>
-      <c r="B59" s="167"/>
-      <c r="C59" s="167"/>
-      <c r="D59" s="167"/>
-      <c r="E59" s="168"/>
-      <c r="F59" s="168"/>
-      <c r="G59" s="168"/>
-      <c r="H59" s="168"/>
-      <c r="I59" s="167"/>
-      <c r="J59" s="169"/>
-      <c r="K59" s="167"/>
+      <c r="A59" s="166"/>
+      <c r="B59" s="168"/>
+      <c r="C59" s="168"/>
+      <c r="D59" s="168"/>
+      <c r="E59" s="169"/>
+      <c r="F59" s="169"/>
+      <c r="G59" s="169"/>
+      <c r="H59" s="169"/>
+      <c r="I59" s="168"/>
+      <c r="J59" s="170"/>
+      <c r="K59" s="168"/>
     </row>
     <row r="60" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="165"/>
-      <c r="B60" s="167"/>
-      <c r="C60" s="167"/>
-      <c r="D60" s="167"/>
-      <c r="E60" s="168"/>
-      <c r="F60" s="168"/>
-      <c r="G60" s="168"/>
-      <c r="H60" s="168"/>
-      <c r="I60" s="167"/>
-      <c r="J60" s="169"/>
-      <c r="K60" s="167"/>
+      <c r="A60" s="166"/>
+      <c r="B60" s="168"/>
+      <c r="C60" s="168"/>
+      <c r="D60" s="168"/>
+      <c r="E60" s="169"/>
+      <c r="F60" s="169"/>
+      <c r="G60" s="169"/>
+      <c r="H60" s="169"/>
+      <c r="I60" s="168"/>
+      <c r="J60" s="170"/>
+      <c r="K60" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5029,7 +5038,7 @@
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="171" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="172" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="7.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="7.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="7.29"/>
@@ -5050,91 +5059,91 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="173"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="174" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="174"/>
+      <c r="B4" s="175"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="175"/>
+      <c r="H4" s="176"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="N4" s="176"/>
+      <c r="N4" s="177"/>
       <c r="P4" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="R4" s="177"/>
+      <c r="R4" s="178"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
@@ -5143,7 +5152,7 @@
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="176" t="s">
+      <c r="F5" s="177" t="s">
         <v>109</v>
       </c>
       <c r="G5" s="7"/>
@@ -5152,220 +5161,220 @@
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
       <c r="N5" s="7"/>
-      <c r="P5" s="178" t="s">
+      <c r="P5" s="179" t="s">
         <v>77</v>
       </c>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="179"/>
+      <c r="Q5" s="179"/>
+      <c r="R5" s="180"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="124" t="s">
+      <c r="A6" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="124"/>
-      <c r="C6" s="180"/>
-      <c r="D6" s="180"/>
-      <c r="E6" s="180"/>
-      <c r="F6" s="180"/>
-      <c r="G6" s="180"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="180"/>
-      <c r="J6" s="180"/>
-      <c r="K6" s="180"/>
-      <c r="L6" s="180"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="180"/>
-      <c r="O6" s="180"/>
-      <c r="P6" s="180"/>
-      <c r="Q6" s="180" t="s">
+      <c r="B6" s="181"/>
+      <c r="C6" s="182"/>
+      <c r="D6" s="182"/>
+      <c r="E6" s="182"/>
+      <c r="F6" s="182"/>
+      <c r="G6" s="182"/>
+      <c r="H6" s="182"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="182"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="182"/>
+      <c r="P6" s="182"/>
+      <c r="Q6" s="182" t="s">
         <v>111</v>
       </c>
-      <c r="R6" s="180" t="s">
+      <c r="R6" s="182" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="124"/>
-      <c r="B7" s="124"/>
-      <c r="C7" s="180"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="180"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="180"/>
-      <c r="J7" s="180"/>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="180"/>
-      <c r="Q7" s="180"/>
-      <c r="R7" s="180"/>
+      <c r="A7" s="181"/>
+      <c r="B7" s="181"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="182"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="182"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="182"/>
+      <c r="R7" s="182"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="124" t="s">
+      <c r="A8" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="180"/>
-      <c r="M8" s="180"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="180"/>
-      <c r="P8" s="180"/>
-      <c r="Q8" s="180"/>
-      <c r="R8" s="180"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="182"/>
+      <c r="Q8" s="182"/>
+      <c r="R8" s="182"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="181" t="s">
+      <c r="B9" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="182" t="s">
+      <c r="C9" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="183" t="s">
+      <c r="D9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="E9" s="183" t="s">
+      <c r="E9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="183" t="s">
+      <c r="F9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="G9" s="183" t="s">
+      <c r="G9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="166" t="s">
+      <c r="H9" s="167" t="s">
         <v>115</v>
       </c>
-      <c r="I9" s="183" t="s">
+      <c r="I9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="183" t="s">
+      <c r="J9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="K9" s="183" t="s">
+      <c r="K9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="183" t="s">
+      <c r="L9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="M9" s="183" t="s">
+      <c r="M9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="183" t="s">
+      <c r="N9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="O9" s="183" t="s">
+      <c r="O9" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="183" t="s">
+      <c r="P9" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="Q9" s="180"/>
-      <c r="R9" s="180"/>
+      <c r="Q9" s="182"/>
+      <c r="R9" s="182"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="184"/>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="100"/>
-      <c r="N10" s="100"/>
-      <c r="O10" s="100"/>
-      <c r="P10" s="100"/>
-      <c r="Q10" s="185"/>
-      <c r="R10" s="186"/>
+      <c r="A10" s="186"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="187"/>
+      <c r="R10" s="188"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="185"/>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="185"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="185"/>
-      <c r="Q11" s="185"/>
-      <c r="R11" s="186"/>
+      <c r="A11" s="187"/>
+      <c r="B11" s="187"/>
+      <c r="C11" s="187"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="187"/>
+      <c r="F11" s="187"/>
+      <c r="G11" s="187"/>
+      <c r="H11" s="187"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="187"/>
+      <c r="K11" s="187"/>
+      <c r="L11" s="187"/>
+      <c r="M11" s="187"/>
+      <c r="N11" s="187"/>
+      <c r="O11" s="187"/>
+      <c r="P11" s="187"/>
+      <c r="Q11" s="187"/>
+      <c r="R11" s="188"/>
     </row>
     <row r="12" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="180" t="s">
+      <c r="A12" s="182" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="180"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="187"/>
-      <c r="R12" s="188"/>
+      <c r="B12" s="182"/>
+      <c r="C12" s="181"/>
+      <c r="D12" s="181"/>
+      <c r="E12" s="181"/>
+      <c r="F12" s="181"/>
+      <c r="G12" s="181"/>
+      <c r="H12" s="181"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="181"/>
+      <c r="L12" s="181"/>
+      <c r="M12" s="181"/>
+      <c r="N12" s="181"/>
+      <c r="O12" s="181"/>
+      <c r="P12" s="181"/>
+      <c r="Q12" s="189"/>
+      <c r="R12" s="190"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="180" t="s">
+      <c r="A13" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="180"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="189"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="181"/>
+      <c r="D13" s="181"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="181"/>
+      <c r="M13" s="181"/>
+      <c r="N13" s="181"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="181"/>
+      <c r="Q13" s="181"/>
+      <c r="R13" s="191"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
-      <c r="B14" s="190"/>
-      <c r="C14" s="190"/>
+      <c r="B14" s="192"/>
+      <c r="C14" s="192"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -5383,344 +5392,344 @@
       <c r="R14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="193" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="191"/>
-      <c r="C15" s="191"/>
-      <c r="D15" s="191"/>
-      <c r="E15" s="191"/>
-      <c r="F15" s="191"/>
-      <c r="G15" s="191"/>
-      <c r="H15" s="191"/>
-      <c r="I15" s="191"/>
-      <c r="J15" s="191"/>
-      <c r="K15" s="191"/>
-      <c r="L15" s="191"/>
-      <c r="M15" s="191"/>
-      <c r="N15" s="191"/>
-      <c r="O15" s="191"/>
-      <c r="P15" s="191"/>
-      <c r="Q15" s="191"/>
+      <c r="B15" s="193"/>
+      <c r="C15" s="193"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="193"/>
+      <c r="G15" s="193"/>
+      <c r="H15" s="193"/>
+      <c r="I15" s="193"/>
+      <c r="J15" s="193"/>
+      <c r="K15" s="193"/>
+      <c r="L15" s="193"/>
+      <c r="M15" s="193"/>
+      <c r="N15" s="193"/>
+      <c r="O15" s="193"/>
+      <c r="P15" s="193"/>
+      <c r="Q15" s="193"/>
       <c r="R15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="189" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="187" t="s">
+      <c r="B16" s="189" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="187"/>
-      <c r="D16" s="187"/>
-      <c r="E16" s="187"/>
-      <c r="F16" s="187"/>
-      <c r="G16" s="187"/>
-      <c r="H16" s="187"/>
-      <c r="I16" s="187"/>
-      <c r="J16" s="187"/>
-      <c r="K16" s="187"/>
-      <c r="L16" s="187"/>
-      <c r="M16" s="187"/>
-      <c r="N16" s="187"/>
-      <c r="O16" s="187"/>
-      <c r="P16" s="187"/>
-      <c r="Q16" s="187"/>
-      <c r="R16" s="187"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+      <c r="F16" s="189"/>
+      <c r="G16" s="189"/>
+      <c r="H16" s="189"/>
+      <c r="I16" s="189"/>
+      <c r="J16" s="189"/>
+      <c r="K16" s="189"/>
+      <c r="L16" s="189"/>
+      <c r="M16" s="189"/>
+      <c r="N16" s="189"/>
+      <c r="O16" s="189"/>
+      <c r="P16" s="189"/>
+      <c r="Q16" s="189"/>
+      <c r="R16" s="189"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="B17" s="192" t="s">
+      <c r="B17" s="194" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="192"/>
-      <c r="D17" s="192"/>
-      <c r="E17" s="192"/>
-      <c r="F17" s="193"/>
-      <c r="G17" s="193"/>
-      <c r="H17" s="193"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="185"/>
-      <c r="K17" s="185"/>
-      <c r="L17" s="185"/>
-      <c r="M17" s="185"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="185"/>
-      <c r="P17" s="185"/>
-      <c r="Q17" s="185"/>
-      <c r="R17" s="185"/>
+      <c r="C17" s="194"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="195"/>
+      <c r="H17" s="195"/>
+      <c r="I17" s="187"/>
+      <c r="J17" s="187"/>
+      <c r="K17" s="187"/>
+      <c r="L17" s="187"/>
+      <c r="M17" s="187"/>
+      <c r="N17" s="187"/>
+      <c r="O17" s="187"/>
+      <c r="P17" s="187"/>
+      <c r="Q17" s="187"/>
+      <c r="R17" s="187"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="194" t="s">
+      <c r="B18" s="196" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="194"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="193"/>
-      <c r="G18" s="193"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="185"/>
-      <c r="L18" s="185"/>
-      <c r="M18" s="185"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="185"/>
-      <c r="P18" s="185"/>
-      <c r="Q18" s="185"/>
-      <c r="R18" s="185"/>
+      <c r="C18" s="196"/>
+      <c r="D18" s="196"/>
+      <c r="E18" s="196"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="195"/>
+      <c r="H18" s="195"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="187"/>
+      <c r="K18" s="187"/>
+      <c r="L18" s="187"/>
+      <c r="M18" s="187"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="187"/>
+      <c r="P18" s="187"/>
+      <c r="Q18" s="187"/>
+      <c r="R18" s="187"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="194" t="s">
+      <c r="B19" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="C19" s="194"/>
-      <c r="D19" s="194"/>
-      <c r="E19" s="194"/>
-      <c r="F19" s="193"/>
-      <c r="G19" s="193"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="195"/>
-      <c r="J19" s="195"/>
-      <c r="K19" s="195"/>
-      <c r="L19" s="195"/>
-      <c r="M19" s="195"/>
-      <c r="N19" s="195"/>
-      <c r="O19" s="195"/>
-      <c r="P19" s="195"/>
-      <c r="Q19" s="195"/>
-      <c r="R19" s="195"/>
-      <c r="S19" s="176"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="195"/>
+      <c r="G19" s="195"/>
+      <c r="H19" s="195"/>
+      <c r="I19" s="197"/>
+      <c r="J19" s="197"/>
+      <c r="K19" s="197"/>
+      <c r="L19" s="197"/>
+      <c r="M19" s="197"/>
+      <c r="N19" s="197"/>
+      <c r="O19" s="197"/>
+      <c r="P19" s="197"/>
+      <c r="Q19" s="197"/>
+      <c r="R19" s="197"/>
+      <c r="S19" s="177"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="194" t="s">
+      <c r="B20" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="194"/>
-      <c r="D20" s="194"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="193" t="s">
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
+      <c r="F20" s="195" t="s">
         <v>125</v>
       </c>
-      <c r="G20" s="193"/>
-      <c r="H20" s="193"/>
-      <c r="I20" s="194" t="s">
+      <c r="G20" s="195"/>
+      <c r="H20" s="195"/>
+      <c r="I20" s="196" t="s">
         <v>126</v>
       </c>
-      <c r="J20" s="194"/>
-      <c r="K20" s="194"/>
-      <c r="L20" s="194"/>
-      <c r="M20" s="194"/>
-      <c r="N20" s="194"/>
-      <c r="O20" s="194"/>
-      <c r="P20" s="194"/>
-      <c r="Q20" s="194"/>
-      <c r="R20" s="194"/>
-      <c r="S20" s="176"/>
+      <c r="J20" s="196"/>
+      <c r="K20" s="196"/>
+      <c r="L20" s="196"/>
+      <c r="M20" s="196"/>
+      <c r="N20" s="196"/>
+      <c r="O20" s="196"/>
+      <c r="P20" s="196"/>
+      <c r="Q20" s="196"/>
+      <c r="R20" s="196"/>
+      <c r="S20" s="177"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="B21" s="194" t="s">
+      <c r="B21" s="196" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="194"/>
-      <c r="D21" s="194"/>
-      <c r="E21" s="194"/>
-      <c r="F21" s="193" t="s">
+      <c r="C21" s="196"/>
+      <c r="D21" s="196"/>
+      <c r="E21" s="196"/>
+      <c r="F21" s="195" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="193"/>
-      <c r="H21" s="193"/>
-      <c r="I21" s="194" t="s">
+      <c r="G21" s="195"/>
+      <c r="H21" s="195"/>
+      <c r="I21" s="196" t="s">
         <v>128</v>
       </c>
-      <c r="J21" s="194"/>
-      <c r="K21" s="194"/>
-      <c r="L21" s="194"/>
-      <c r="M21" s="194"/>
-      <c r="N21" s="194"/>
-      <c r="O21" s="194"/>
-      <c r="P21" s="194"/>
-      <c r="Q21" s="194"/>
-      <c r="R21" s="194"/>
+      <c r="J21" s="196"/>
+      <c r="K21" s="196"/>
+      <c r="L21" s="196"/>
+      <c r="M21" s="196"/>
+      <c r="N21" s="196"/>
+      <c r="O21" s="196"/>
+      <c r="P21" s="196"/>
+      <c r="Q21" s="196"/>
+      <c r="R21" s="196"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="B22" s="194" t="s">
+      <c r="B22" s="196" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="194"/>
-      <c r="D22" s="194"/>
-      <c r="E22" s="194"/>
-      <c r="F22" s="193" t="s">
+      <c r="C22" s="196"/>
+      <c r="D22" s="196"/>
+      <c r="E22" s="196"/>
+      <c r="F22" s="195" t="s">
         <v>125</v>
       </c>
-      <c r="G22" s="193"/>
-      <c r="H22" s="193"/>
-      <c r="I22" s="194"/>
-      <c r="J22" s="194"/>
-      <c r="K22" s="194"/>
-      <c r="L22" s="194"/>
-      <c r="M22" s="194"/>
-      <c r="N22" s="194"/>
-      <c r="O22" s="194"/>
-      <c r="P22" s="194"/>
-      <c r="Q22" s="194"/>
-      <c r="R22" s="194"/>
+      <c r="G22" s="195"/>
+      <c r="H22" s="195"/>
+      <c r="I22" s="196"/>
+      <c r="J22" s="196"/>
+      <c r="K22" s="196"/>
+      <c r="L22" s="196"/>
+      <c r="M22" s="196"/>
+      <c r="N22" s="196"/>
+      <c r="O22" s="196"/>
+      <c r="P22" s="196"/>
+      <c r="Q22" s="196"/>
+      <c r="R22" s="196"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="B23" s="194" t="s">
+      <c r="B23" s="196" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="194"/>
-      <c r="D23" s="194"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="193"/>
-      <c r="G23" s="193"/>
-      <c r="H23" s="193"/>
-      <c r="I23" s="194" t="s">
+      <c r="C23" s="196"/>
+      <c r="D23" s="196"/>
+      <c r="E23" s="196"/>
+      <c r="F23" s="195"/>
+      <c r="G23" s="195"/>
+      <c r="H23" s="195"/>
+      <c r="I23" s="196" t="s">
         <v>131</v>
       </c>
-      <c r="J23" s="194"/>
-      <c r="K23" s="194"/>
-      <c r="L23" s="194"/>
-      <c r="M23" s="194"/>
-      <c r="N23" s="194"/>
-      <c r="O23" s="194"/>
-      <c r="P23" s="194"/>
-      <c r="Q23" s="194"/>
-      <c r="R23" s="194"/>
+      <c r="J23" s="196"/>
+      <c r="K23" s="196"/>
+      <c r="L23" s="196"/>
+      <c r="M23" s="196"/>
+      <c r="N23" s="196"/>
+      <c r="O23" s="196"/>
+      <c r="P23" s="196"/>
+      <c r="Q23" s="196"/>
+      <c r="R23" s="196"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="194" t="s">
+      <c r="B24" s="196" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="194"/>
-      <c r="D24" s="194"/>
-      <c r="E24" s="194"/>
-      <c r="F24" s="193"/>
-      <c r="G24" s="193"/>
-      <c r="H24" s="193"/>
-      <c r="I24" s="194" t="s">
+      <c r="C24" s="196"/>
+      <c r="D24" s="196"/>
+      <c r="E24" s="196"/>
+      <c r="F24" s="195"/>
+      <c r="G24" s="195"/>
+      <c r="H24" s="195"/>
+      <c r="I24" s="196" t="s">
         <v>131</v>
       </c>
-      <c r="J24" s="194"/>
-      <c r="K24" s="194"/>
-      <c r="L24" s="194"/>
-      <c r="M24" s="194"/>
-      <c r="N24" s="194"/>
-      <c r="O24" s="194"/>
-      <c r="P24" s="194"/>
-      <c r="Q24" s="194"/>
-      <c r="R24" s="194"/>
+      <c r="J24" s="196"/>
+      <c r="K24" s="196"/>
+      <c r="L24" s="196"/>
+      <c r="M24" s="196"/>
+      <c r="N24" s="196"/>
+      <c r="O24" s="196"/>
+      <c r="P24" s="196"/>
+      <c r="Q24" s="196"/>
+      <c r="R24" s="196"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="B25" s="194" t="s">
+      <c r="B25" s="196" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="194"/>
-      <c r="D25" s="194"/>
-      <c r="E25" s="194"/>
-      <c r="F25" s="196"/>
-      <c r="G25" s="196"/>
-      <c r="H25" s="196"/>
-      <c r="I25" s="195"/>
-      <c r="J25" s="195"/>
-      <c r="K25" s="195"/>
-      <c r="L25" s="195"/>
-      <c r="M25" s="195"/>
-      <c r="N25" s="195"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="195"/>
-      <c r="Q25" s="195"/>
-      <c r="R25" s="195"/>
+      <c r="C25" s="196"/>
+      <c r="D25" s="196"/>
+      <c r="E25" s="196"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="198"/>
+      <c r="H25" s="198"/>
+      <c r="I25" s="197"/>
+      <c r="J25" s="197"/>
+      <c r="K25" s="197"/>
+      <c r="L25" s="197"/>
+      <c r="M25" s="197"/>
+      <c r="N25" s="197"/>
+      <c r="O25" s="197"/>
+      <c r="P25" s="197"/>
+      <c r="Q25" s="197"/>
+      <c r="R25" s="197"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="B26" s="194" t="s">
+      <c r="B26" s="196" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="194"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="194"/>
-      <c r="I26" s="194"/>
-      <c r="J26" s="194"/>
-      <c r="K26" s="194"/>
-      <c r="L26" s="194"/>
-      <c r="M26" s="194"/>
-      <c r="N26" s="194"/>
-      <c r="O26" s="194"/>
-      <c r="P26" s="194"/>
-      <c r="Q26" s="194"/>
-      <c r="R26" s="194"/>
+      <c r="C26" s="196"/>
+      <c r="D26" s="196"/>
+      <c r="E26" s="196"/>
+      <c r="F26" s="196"/>
+      <c r="G26" s="196"/>
+      <c r="H26" s="196"/>
+      <c r="I26" s="196"/>
+      <c r="J26" s="196"/>
+      <c r="K26" s="196"/>
+      <c r="L26" s="196"/>
+      <c r="M26" s="196"/>
+      <c r="N26" s="196"/>
+      <c r="O26" s="196"/>
+      <c r="P26" s="196"/>
+      <c r="Q26" s="196"/>
+      <c r="R26" s="196"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="187" t="s">
+      <c r="A27" s="189" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="187" t="s">
+      <c r="B27" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="187"/>
-      <c r="D27" s="187"/>
-      <c r="E27" s="187"/>
-      <c r="F27" s="187"/>
-      <c r="G27" s="187"/>
-      <c r="H27" s="187"/>
-      <c r="I27" s="187"/>
-      <c r="J27" s="187"/>
-      <c r="K27" s="187"/>
-      <c r="L27" s="187"/>
-      <c r="M27" s="187"/>
-      <c r="N27" s="187"/>
-      <c r="O27" s="187"/>
-      <c r="P27" s="187"/>
-      <c r="Q27" s="187"/>
-      <c r="R27" s="187"/>
+      <c r="C27" s="189"/>
+      <c r="D27" s="189"/>
+      <c r="E27" s="189"/>
+      <c r="F27" s="189"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="189"/>
+      <c r="I27" s="189"/>
+      <c r="J27" s="189"/>
+      <c r="K27" s="189"/>
+      <c r="L27" s="189"/>
+      <c r="M27" s="189"/>
+      <c r="N27" s="189"/>
+      <c r="O27" s="189"/>
+      <c r="P27" s="189"/>
+      <c r="Q27" s="189"/>
+      <c r="R27" s="189"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="185" t="n">
+      <c r="A28" s="187" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="194" t="s">
+      <c r="B28" s="196" t="s">
         <v>137</v>
       </c>
-      <c r="C28" s="194"/>
-      <c r="D28" s="194"/>
-      <c r="E28" s="194"/>
-      <c r="F28" s="193"/>
-      <c r="G28" s="193"/>
-      <c r="H28" s="193"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="195"/>
+      <c r="G28" s="195"/>
+      <c r="H28" s="195"/>
       <c r="I28" s="65"/>
       <c r="J28" s="65"/>
       <c r="K28" s="65"/>
@@ -5733,161 +5742,161 @@
       <c r="R28" s="65"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="185" t="n">
+      <c r="A29" s="187" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="194" t="s">
+      <c r="B29" s="196" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="194"/>
-      <c r="D29" s="194"/>
-      <c r="E29" s="194"/>
-      <c r="F29" s="193"/>
-      <c r="G29" s="193"/>
-      <c r="H29" s="193"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
-      <c r="N29" s="185"/>
-      <c r="O29" s="185"/>
-      <c r="P29" s="185"/>
-      <c r="Q29" s="185"/>
-      <c r="R29" s="185"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="195"/>
+      <c r="G29" s="195"/>
+      <c r="H29" s="195"/>
+      <c r="I29" s="187"/>
+      <c r="J29" s="187"/>
+      <c r="K29" s="187"/>
+      <c r="L29" s="187"/>
+      <c r="M29" s="187"/>
+      <c r="N29" s="187"/>
+      <c r="O29" s="187"/>
+      <c r="P29" s="187"/>
+      <c r="Q29" s="187"/>
+      <c r="R29" s="187"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="185" t="n">
+      <c r="A30" s="187" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="194" t="s">
+      <c r="B30" s="196" t="s">
         <v>139</v>
       </c>
-      <c r="C30" s="194"/>
-      <c r="D30" s="194"/>
-      <c r="E30" s="194"/>
-      <c r="F30" s="193"/>
-      <c r="G30" s="193"/>
-      <c r="H30" s="193"/>
-      <c r="I30" s="195"/>
-      <c r="J30" s="195"/>
-      <c r="K30" s="195"/>
-      <c r="L30" s="195"/>
-      <c r="M30" s="195"/>
-      <c r="N30" s="195"/>
-      <c r="O30" s="195"/>
-      <c r="P30" s="195"/>
-      <c r="Q30" s="195"/>
-      <c r="R30" s="195"/>
+      <c r="C30" s="196"/>
+      <c r="D30" s="196"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="195"/>
+      <c r="G30" s="195"/>
+      <c r="H30" s="195"/>
+      <c r="I30" s="197"/>
+      <c r="J30" s="197"/>
+      <c r="K30" s="197"/>
+      <c r="L30" s="197"/>
+      <c r="M30" s="197"/>
+      <c r="N30" s="197"/>
+      <c r="O30" s="197"/>
+      <c r="P30" s="197"/>
+      <c r="Q30" s="197"/>
+      <c r="R30" s="197"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="185" t="n">
+      <c r="A31" s="187" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="197" t="s">
+      <c r="B31" s="199" t="s">
         <v>140</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
-      <c r="E31" s="198"/>
-      <c r="F31" s="193" t="str">
+      <c r="E31" s="200"/>
+      <c r="F31" s="195" t="str">
         <f aca="true" t="array" ref="F31:F31">IFERROR(INDIRECT("'" &amp; R4-1 &amp; "'!F173") - R13, "-")</f>
         <v>-</v>
       </c>
-      <c r="G31" s="193"/>
-      <c r="H31" s="193"/>
-      <c r="I31" s="194" t="s">
+      <c r="G31" s="195"/>
+      <c r="H31" s="195"/>
+      <c r="I31" s="196" t="s">
         <v>141</v>
       </c>
-      <c r="J31" s="194"/>
-      <c r="K31" s="194"/>
-      <c r="L31" s="194"/>
-      <c r="M31" s="194"/>
-      <c r="N31" s="194"/>
-      <c r="O31" s="194"/>
-      <c r="P31" s="194"/>
-      <c r="Q31" s="194"/>
-      <c r="R31" s="194"/>
+      <c r="J31" s="196"/>
+      <c r="K31" s="196"/>
+      <c r="L31" s="196"/>
+      <c r="M31" s="196"/>
+      <c r="N31" s="196"/>
+      <c r="O31" s="196"/>
+      <c r="P31" s="196"/>
+      <c r="Q31" s="196"/>
+      <c r="R31" s="196"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="185" t="n">
+      <c r="A32" s="187" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="199" t="s">
+      <c r="B32" s="201" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="199"/>
-      <c r="D32" s="199"/>
-      <c r="E32" s="199"/>
-      <c r="F32" s="199"/>
-      <c r="G32" s="199"/>
-      <c r="H32" s="199"/>
-      <c r="I32" s="199"/>
-      <c r="J32" s="199"/>
-      <c r="K32" s="199"/>
-      <c r="L32" s="199"/>
-      <c r="M32" s="199"/>
-      <c r="N32" s="199"/>
-      <c r="O32" s="199"/>
-      <c r="P32" s="199"/>
-      <c r="Q32" s="199"/>
-      <c r="R32" s="199"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="201"/>
+      <c r="E32" s="201"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="201"/>
+      <c r="I32" s="201"/>
+      <c r="J32" s="201"/>
+      <c r="K32" s="201"/>
+      <c r="L32" s="201"/>
+      <c r="M32" s="201"/>
+      <c r="N32" s="201"/>
+      <c r="O32" s="201"/>
+      <c r="P32" s="201"/>
+      <c r="Q32" s="201"/>
+      <c r="R32" s="201"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c r="E47" s="200"/>
+      <c r="E47" s="202"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="200"/>
+      <c r="G47" s="202"/>
       <c r="H47" s="7"/>
-      <c r="I47" s="200"/>
+      <c r="I47" s="202"/>
       <c r="J47" s="7"/>
-      <c r="K47" s="200"/>
+      <c r="K47" s="202"/>
       <c r="L47" s="7"/>
-      <c r="M47" s="201"/>
+      <c r="M47" s="203"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="177"/>
+      <c r="P47" s="178"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E48" s="202"/>
-      <c r="G48" s="202"/>
-      <c r="I48" s="202"/>
-      <c r="K48" s="202"/>
-      <c r="M48" s="201"/>
-      <c r="P48" s="177"/>
+      <c r="E48" s="204"/>
+      <c r="G48" s="204"/>
+      <c r="I48" s="204"/>
+      <c r="K48" s="204"/>
+      <c r="M48" s="203"/>
+      <c r="P48" s="178"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P49" s="177"/>
+      <c r="P49" s="178"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
-      <c r="E66" s="200"/>
+      <c r="E66" s="202"/>
       <c r="F66" s="7"/>
-      <c r="G66" s="200"/>
+      <c r="G66" s="202"/>
       <c r="H66" s="7"/>
-      <c r="I66" s="200"/>
+      <c r="I66" s="202"/>
       <c r="J66" s="7"/>
-      <c r="K66" s="200"/>
+      <c r="K66" s="202"/>
       <c r="L66" s="7"/>
-      <c r="M66" s="201"/>
+      <c r="M66" s="203"/>
       <c r="N66" s="7"/>
       <c r="O66" s="7"/>
-      <c r="P66" s="177"/>
+      <c r="P66" s="178"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E67" s="202"/>
-      <c r="G67" s="202"/>
-      <c r="I67" s="202"/>
-      <c r="K67" s="202"/>
-      <c r="M67" s="201"/>
-      <c r="P67" s="177"/>
+      <c r="E67" s="204"/>
+      <c r="G67" s="204"/>
+      <c r="I67" s="204"/>
+      <c r="K67" s="204"/>
+      <c r="M67" s="203"/>
+      <c r="P67" s="178"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P68" s="177"/>
+      <c r="P68" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="69">
@@ -5988,14 +5997,14 @@
   </cols>
   <sheetData>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="203"/>
+      <c r="B6" s="205"/>
       <c r="D6" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="204"/>
+      <c r="E6" s="206"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="205"/>
+      <c r="E7" s="207"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="60" t="s">
@@ -6018,206 +6027,206 @@
       <c r="D10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="206" t="s">
+      <c r="A11" s="208" t="s">
         <v>147</v>
       </c>
-      <c r="B11" s="206"/>
-      <c r="C11" s="206"/>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
+      <c r="B11" s="208"/>
+      <c r="C11" s="208"/>
+      <c r="D11" s="208"/>
+      <c r="E11" s="208"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="175" t="s">
+      <c r="B13" s="176" t="s">
         <v>148</v>
       </c>
       <c r="C13" s="84"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="208"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="210"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="209"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="211"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="177"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="213"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="212" t="s">
+      <c r="A15" s="214" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="213" t="s">
+      <c r="B15" s="215" t="s">
         <v>149</v>
       </c>
-      <c r="C15" s="213" t="s">
+      <c r="C15" s="215" t="s">
         <v>150</v>
       </c>
-      <c r="D15" s="213" t="s">
+      <c r="D15" s="215" t="s">
         <v>151</v>
       </c>
-      <c r="E15" s="213" t="s">
+      <c r="E15" s="215" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="165" t="n">
+      <c r="A16" s="166" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="151"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="165"/>
-      <c r="E16" s="165"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="166"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="165" t="n">
+      <c r="A17" s="166" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="151"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="165"/>
-      <c r="E17" s="165"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="166"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="165" t="n">
+      <c r="A18" s="166" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="151"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="165"/>
-      <c r="E18" s="165"/>
+      <c r="B18" s="152"/>
+      <c r="C18" s="166"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="165" t="n">
+      <c r="A19" s="166" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="151"/>
-      <c r="C19" s="165"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
+      <c r="B19" s="152"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="166"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="165" t="n">
+      <c r="A20" s="166" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="151"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
+      <c r="B20" s="152"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="166"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="165" t="n">
+      <c r="A21" s="166" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="151"/>
-      <c r="C21" s="165"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="165"/>
+      <c r="B21" s="152"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="165" t="n">
+      <c r="A22" s="166" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="151"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="165"/>
+      <c r="B22" s="152"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="165" t="n">
+      <c r="A23" s="166" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="151"/>
-      <c r="C23" s="165"/>
-      <c r="D23" s="165"/>
-      <c r="E23" s="165"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="165" t="n">
+      <c r="A24" s="166" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="151"/>
-      <c r="C24" s="165"/>
-      <c r="D24" s="165"/>
-      <c r="E24" s="165"/>
+      <c r="B24" s="152"/>
+      <c r="C24" s="166"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="166"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="165" t="n">
+      <c r="A25" s="166" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="165"/>
-      <c r="D25" s="165"/>
-      <c r="E25" s="165"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="166"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="166"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="165" t="n">
+      <c r="A26" s="166" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="151"/>
-      <c r="C26" s="165"/>
-      <c r="D26" s="165"/>
-      <c r="E26" s="165"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="166"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="165" t="n">
+      <c r="A27" s="166" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="151"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="166"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="165" t="n">
+      <c r="A28" s="166" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="151"/>
-      <c r="C28" s="165"/>
-      <c r="D28" s="165"/>
-      <c r="E28" s="165"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="165" t="n">
+      <c r="A29" s="166" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="151"/>
-      <c r="C29" s="165"/>
-      <c r="D29" s="165"/>
-      <c r="E29" s="165"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="166"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="166"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="165" t="n">
+      <c r="A30" s="166" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="151"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="165"/>
-      <c r="E30" s="165"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="166"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="166"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="165" t="n">
+      <c r="A31" s="166" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="151"/>
-      <c r="C31" s="165"/>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="165" t="n">
+      <c r="A32" s="166" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="151"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
+      <c r="B32" s="152"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E36" s="214"/>
+      <c r="E36" s="216"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="215"/>
+      <c r="E38" s="217"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="214"/>
+      <c r="E39" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6243,7 +6252,7 @@
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="5.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="171" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="172" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="5.71"/>
@@ -6264,70 +6273,70 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="173"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="172"/>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
-      <c r="N2" s="172"/>
-      <c r="O2" s="172"/>
-      <c r="P2" s="172"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
+      <c r="N2" s="173"/>
+      <c r="O2" s="173"/>
+      <c r="P2" s="173"/>
+      <c r="Q2" s="173"/>
+      <c r="R2" s="173"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="174" t="s">
         <v>152</v>
       </c>
-      <c r="B3" s="173"/>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
-      <c r="O3" s="173"/>
-      <c r="P3" s="173"/>
-      <c r="Q3" s="173"/>
-      <c r="R3" s="173"/>
+      <c r="B3" s="174"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="7"/>
@@ -6335,7 +6344,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="175"/>
+      <c r="H4" s="176"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -6349,7 +6358,7 @@
       <c r="A5" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="174"/>
+      <c r="B5" s="175"/>
       <c r="C5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -6358,12 +6367,12 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="N5" s="176"/>
+      <c r="N5" s="177"/>
       <c r="Q5" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="R5" s="176"/>
-      <c r="S5" s="216"/>
+      <c r="R5" s="177"/>
+      <c r="S5" s="218"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
@@ -6373,13 +6382,13 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="176" t="s">
+      <c r="H6" s="177" t="s">
         <v>109</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="N6" s="175"/>
+      <c r="N6" s="176"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
         <v>77</v>
@@ -6387,215 +6396,215 @@
       <c r="R6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="124" t="s">
+      <c r="A7" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="124"/>
-      <c r="C7" s="180"/>
-      <c r="D7" s="180"/>
-      <c r="E7" s="180"/>
-      <c r="F7" s="180"/>
-      <c r="G7" s="180"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="180"/>
-      <c r="J7" s="180"/>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="180"/>
-      <c r="Q7" s="180" t="s">
+      <c r="B7" s="181"/>
+      <c r="C7" s="182"/>
+      <c r="D7" s="182"/>
+      <c r="E7" s="182"/>
+      <c r="F7" s="182"/>
+      <c r="G7" s="182"/>
+      <c r="H7" s="182"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="182"/>
+      <c r="K7" s="182"/>
+      <c r="L7" s="182"/>
+      <c r="M7" s="182"/>
+      <c r="N7" s="182"/>
+      <c r="O7" s="182"/>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="182" t="s">
         <v>153</v>
       </c>
-      <c r="R7" s="180" t="s">
+      <c r="R7" s="182" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="124"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="180"/>
-      <c r="M8" s="180"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="180"/>
-      <c r="P8" s="180"/>
-      <c r="Q8" s="180"/>
-      <c r="R8" s="180"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="181"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="182"/>
+      <c r="E8" s="182"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="182"/>
+      <c r="H8" s="182"/>
+      <c r="I8" s="182"/>
+      <c r="J8" s="182"/>
+      <c r="K8" s="182"/>
+      <c r="L8" s="182"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="182"/>
+      <c r="Q8" s="182"/>
+      <c r="R8" s="182"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="124" t="s">
+      <c r="A9" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="180"/>
-      <c r="E9" s="180"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="180"/>
-      <c r="H9" s="180"/>
-      <c r="I9" s="180"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="180"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="180"/>
-      <c r="P9" s="180"/>
-      <c r="Q9" s="180"/>
-      <c r="R9" s="180"/>
+      <c r="B9" s="181"/>
+      <c r="C9" s="182"/>
+      <c r="D9" s="182"/>
+      <c r="E9" s="182"/>
+      <c r="F9" s="182"/>
+      <c r="G9" s="182"/>
+      <c r="H9" s="182"/>
+      <c r="I9" s="182"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="182"/>
+      <c r="L9" s="182"/>
+      <c r="M9" s="182"/>
+      <c r="N9" s="182"/>
+      <c r="O9" s="182"/>
+      <c r="P9" s="182"/>
+      <c r="Q9" s="182"/>
+      <c r="R9" s="182"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="180" t="s">
+      <c r="B10" s="182" t="s">
         <v>114</v>
       </c>
-      <c r="C10" s="182" t="s">
+      <c r="C10" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="183" t="s">
+      <c r="D10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="E10" s="183" t="s">
+      <c r="E10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="183" t="s">
+      <c r="F10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="183" t="s">
+      <c r="G10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="183" t="s">
+      <c r="H10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="I10" s="183" t="s">
+      <c r="I10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="183" t="s">
+      <c r="J10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="K10" s="183" t="s">
+      <c r="K10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="183" t="s">
+      <c r="L10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="M10" s="183" t="s">
+      <c r="M10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="N10" s="183" t="s">
+      <c r="N10" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="O10" s="183" t="s">
+      <c r="O10" s="185" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="183" t="s">
+      <c r="P10" s="185" t="s">
         <v>154</v>
       </c>
-      <c r="Q10" s="180"/>
-      <c r="R10" s="180"/>
+      <c r="Q10" s="182"/>
+      <c r="R10" s="182"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="124"/>
-      <c r="B11" s="217"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="124"/>
+      <c r="A11" s="181"/>
+      <c r="B11" s="219"/>
+      <c r="C11" s="181"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
       <c r="H11" s="76"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="185"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="185"/>
-      <c r="Q11" s="185"/>
-      <c r="R11" s="186"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="187"/>
+      <c r="K11" s="187"/>
+      <c r="L11" s="187"/>
+      <c r="M11" s="187"/>
+      <c r="N11" s="187"/>
+      <c r="O11" s="187"/>
+      <c r="P11" s="187"/>
+      <c r="Q11" s="187"/>
+      <c r="R11" s="188"/>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="185" t="s">
+      <c r="A12" s="187" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="185"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
-      <c r="N12" s="185"/>
-      <c r="O12" s="185"/>
-      <c r="P12" s="185"/>
-      <c r="Q12" s="187"/>
-      <c r="R12" s="218"/>
+      <c r="B12" s="187"/>
+      <c r="C12" s="187"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="187"/>
+      <c r="J12" s="187"/>
+      <c r="K12" s="187"/>
+      <c r="L12" s="187"/>
+      <c r="M12" s="187"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="187"/>
+      <c r="P12" s="187"/>
+      <c r="Q12" s="189"/>
+      <c r="R12" s="220"/>
     </row>
     <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="180" t="s">
+      <c r="A13" s="182" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="180"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="185"/>
-      <c r="R13" s="219"/>
+      <c r="B13" s="182"/>
+      <c r="C13" s="181"/>
+      <c r="D13" s="181"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="181"/>
+      <c r="L13" s="181"/>
+      <c r="M13" s="181"/>
+      <c r="N13" s="181"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="181"/>
+      <c r="Q13" s="187"/>
+      <c r="R13" s="221"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="180" t="s">
+      <c r="A14" s="182" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="180"/>
-      <c r="C14" s="124"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="124"/>
-      <c r="Q14" s="124"/>
-      <c r="R14" s="188"/>
+      <c r="B14" s="182"/>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="181"/>
+      <c r="M14" s="181"/>
+      <c r="N14" s="181"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="181"/>
+      <c r="Q14" s="181"/>
+      <c r="R14" s="190"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
-      <c r="B15" s="190"/>
-      <c r="C15" s="190"/>
+      <c r="B15" s="192"/>
+      <c r="C15" s="192"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -6632,8 +6641,8 @@
       <c r="R16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="220"/>
-      <c r="B17" s="221"/>
+      <c r="A17" s="222"/>
+      <c r="B17" s="223"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -6649,16 +6658,16 @@
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
-      <c r="R17" s="220"/>
+      <c r="R17" s="222"/>
       <c r="S17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Q18" s="177"/>
-      <c r="R18" s="177"/>
-      <c r="S18" s="177"/>
+      <c r="Q18" s="178"/>
+      <c r="R18" s="178"/>
+      <c r="S18" s="178"/>
     </row>
     <row r="21" s="60" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="171"/>
+      <c r="C21" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -6706,64 +6715,64 @@
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="222" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="222" width="27.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="222" width="35.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="222" width="7.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="222" width="7.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="222" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="222" width="30.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="222" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="222" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="222" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="222" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="224" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="224" width="27.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="224" width="35.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="224" width="7.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="224" width="7.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="224" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="224" width="30.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="224" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="224" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="224" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="224" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="223"/>
-      <c r="B1" s="223"/>
-      <c r="C1" s="224" t="s">
+      <c r="A1" s="225"/>
+      <c r="B1" s="225"/>
+      <c r="C1" s="226" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
     </row>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="226"/>
-      <c r="B2" s="226"/>
-      <c r="C2" s="227" t="s">
+      <c r="A2" s="228"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="229" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="227"/>
-      <c r="E2" s="227"/>
-      <c r="F2" s="227"/>
-      <c r="G2" s="227"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="228"/>
-      <c r="J2" s="228"/>
+      <c r="D2" s="229"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="229"/>
+      <c r="I2" s="230"/>
+      <c r="J2" s="230"/>
     </row>
     <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="226"/>
-      <c r="B3" s="226"/>
-      <c r="C3" s="229" t="s">
+      <c r="A3" s="228"/>
+      <c r="B3" s="228"/>
+      <c r="C3" s="231" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
-      <c r="F3" s="229"/>
-      <c r="G3" s="229"/>
-      <c r="H3" s="229"/>
-      <c r="I3" s="230"/>
-      <c r="J3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="231"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="233"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="226"/>
-      <c r="B4" s="226"/>
+      <c r="A4" s="228"/>
+      <c r="B4" s="228"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
@@ -6771,19 +6780,19 @@
       <c r="G4" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="234" t="s">
         <v>158</v>
       </c>
-      <c r="I4" s="232" t="s">
+      <c r="I4" s="234" t="s">
         <v>159</v>
       </c>
-      <c r="J4" s="233" t="s">
+      <c r="J4" s="235" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="226"/>
-      <c r="B5" s="226"/>
+      <c r="A5" s="228"/>
+      <c r="B5" s="228"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
@@ -6791,139 +6800,139 @@
       <c r="G5" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="H5" s="234"/>
-      <c r="I5" s="234"/>
-      <c r="J5" s="233"/>
+      <c r="H5" s="236"/>
+      <c r="I5" s="236"/>
+      <c r="J5" s="235"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="235"/>
-      <c r="B6" s="235"/>
-      <c r="C6" s="235"/>
-      <c r="D6" s="235"/>
-      <c r="E6" s="235"/>
-      <c r="F6" s="235"/>
+      <c r="A6" s="237"/>
+      <c r="B6" s="237"/>
+      <c r="C6" s="237"/>
+      <c r="D6" s="237"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="237"/>
       <c r="G6" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="234"/>
-      <c r="I6" s="234"/>
-      <c r="J6" s="233"/>
+      <c r="H6" s="236"/>
+      <c r="I6" s="236"/>
+      <c r="J6" s="235"/>
     </row>
     <row r="7" customFormat="false" ht="25.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="236" t="s">
+      <c r="A7" s="238" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="239" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="237" t="s">
+      <c r="C7" s="239" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="237" t="s">
+      <c r="D7" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="237" t="s">
+      <c r="E7" s="239" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="238"/>
-      <c r="G7" s="238" t="s">
+      <c r="F7" s="240"/>
+      <c r="G7" s="240" t="s">
         <v>166</v>
       </c>
-      <c r="H7" s="238" t="s">
+      <c r="H7" s="240" t="s">
         <v>167</v>
       </c>
-      <c r="I7" s="238"/>
-      <c r="J7" s="239" t="s">
+      <c r="I7" s="240"/>
+      <c r="J7" s="241" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="240"/>
+      <c r="A8" s="242"/>
       <c r="B8" s="82"/>
       <c r="C8" s="82"/>
       <c r="D8" s="84"/>
       <c r="E8" s="84"/>
-      <c r="F8" s="241"/>
-      <c r="G8" s="241"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
       <c r="H8" s="87"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="243"/>
+      <c r="I8" s="244"/>
+      <c r="J8" s="245"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="244"/>
-      <c r="B9" s="245"/>
+      <c r="A9" s="246"/>
+      <c r="B9" s="247"/>
       <c r="C9" s="65" t="s">
         <v>168</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="186"/>
-      <c r="H9" s="124"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="247"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="188"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="181"/>
+      <c r="J9" s="249"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="244"/>
-      <c r="B10" s="245"/>
+      <c r="A10" s="246"/>
+      <c r="B10" s="247"/>
       <c r="C10" s="65" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
-      <c r="F10" s="246" t="n">
+      <c r="F10" s="248" t="n">
         <f aca="false">F9*1.13</f>
         <v>0</v>
       </c>
-      <c r="G10" s="186"/>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="248"/>
+      <c r="G10" s="188"/>
+      <c r="H10" s="181"/>
+      <c r="I10" s="181"/>
+      <c r="J10" s="250"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="249"/>
-      <c r="B11" s="250"/>
-      <c r="C11" s="251" t="s">
+      <c r="A11" s="251"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="253" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="252" t="n">
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="254" t="n">
         <f aca="false">F9+F10</f>
         <v>0</v>
       </c>
-      <c r="G11" s="253"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="247"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="187"/>
+      <c r="I11" s="187"/>
+      <c r="J11" s="249"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="254"/>
+      <c r="A12" s="256"/>
       <c r="B12" s="7"/>
-      <c r="C12" s="255"/>
-      <c r="D12" s="255"/>
-      <c r="E12" s="255"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="257"/>
-      <c r="H12" s="171"/>
-      <c r="I12" s="171"/>
-      <c r="J12" s="258"/>
+      <c r="C12" s="257"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="257"/>
+      <c r="F12" s="258"/>
+      <c r="G12" s="259"/>
+      <c r="H12" s="172"/>
+      <c r="I12" s="172"/>
+      <c r="J12" s="260"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="254"/>
+      <c r="A13" s="256"/>
       <c r="B13" s="7"/>
-      <c r="C13" s="255"/>
-      <c r="D13" s="255"/>
-      <c r="E13" s="255"/>
-      <c r="F13" s="256"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="171"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="258"/>
+      <c r="C13" s="257"/>
+      <c r="D13" s="257"/>
+      <c r="E13" s="257"/>
+      <c r="F13" s="258"/>
+      <c r="G13" s="259"/>
+      <c r="H13" s="172"/>
+      <c r="I13" s="172"/>
+      <c r="J13" s="260"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="259"/>
-      <c r="B14" s="259"/>
+      <c r="A14" s="261"/>
+      <c r="B14" s="261"/>
       <c r="C14" s="60"/>
       <c r="D14" s="60"/>
       <c r="E14" s="60"/>
@@ -6931,146 +6940,146 @@
       <c r="G14" s="60"/>
       <c r="H14" s="60"/>
       <c r="I14" s="60"/>
-      <c r="J14" s="260"/>
+      <c r="J14" s="262"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="261" t="s">
+      <c r="A15" s="263" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="261"/>
-      <c r="C15" s="262" t="s">
+      <c r="B15" s="263"/>
+      <c r="C15" s="264" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="262"/>
-      <c r="E15" s="262"/>
+      <c r="D15" s="264"/>
+      <c r="E15" s="264"/>
       <c r="F15" s="36"/>
-      <c r="G15" s="263" t="s">
+      <c r="G15" s="265" t="s">
         <v>171</v>
       </c>
-      <c r="H15" s="263"/>
-      <c r="I15" s="262"/>
-      <c r="J15" s="262"/>
-      <c r="K15" s="264"/>
+      <c r="H15" s="265"/>
+      <c r="I15" s="264"/>
+      <c r="J15" s="264"/>
+      <c r="K15" s="266"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="265"/>
-      <c r="B16" s="265"/>
+      <c r="A16" s="267"/>
+      <c r="B16" s="267"/>
       <c r="C16" s="45"/>
       <c r="D16" s="45"/>
       <c r="E16" s="45"/>
       <c r="F16" s="36"/>
-      <c r="G16" s="263" t="s">
+      <c r="G16" s="265" t="s">
         <v>172</v>
       </c>
-      <c r="H16" s="263"/>
-      <c r="I16" s="262"/>
-      <c r="J16" s="262"/>
+      <c r="H16" s="265"/>
+      <c r="I16" s="264"/>
+      <c r="J16" s="264"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="266" t="s">
+      <c r="A17" s="268" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="266"/>
-      <c r="C17" s="267" t="s">
+      <c r="B17" s="268"/>
+      <c r="C17" s="269" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="267"/>
-      <c r="E17" s="267"/>
+      <c r="D17" s="269"/>
+      <c r="E17" s="269"/>
       <c r="F17" s="36"/>
-      <c r="G17" s="263" t="s">
+      <c r="G17" s="265" t="s">
         <v>175</v>
       </c>
-      <c r="H17" s="263"/>
-      <c r="I17" s="262"/>
-      <c r="J17" s="262"/>
+      <c r="H17" s="265"/>
+      <c r="I17" s="264"/>
+      <c r="J17" s="264"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="268"/>
-      <c r="B18" s="268"/>
-      <c r="C18" s="269"/>
-      <c r="D18" s="269"/>
-      <c r="E18" s="269"/>
+      <c r="A18" s="270"/>
+      <c r="B18" s="270"/>
+      <c r="C18" s="271"/>
+      <c r="D18" s="271"/>
+      <c r="E18" s="271"/>
       <c r="F18" s="60"/>
-      <c r="G18" s="263" t="s">
+      <c r="G18" s="265" t="s">
         <v>176</v>
       </c>
-      <c r="H18" s="263"/>
-      <c r="I18" s="262"/>
-      <c r="J18" s="262"/>
+      <c r="H18" s="265"/>
+      <c r="I18" s="264"/>
+      <c r="J18" s="264"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="270" t="s">
+      <c r="A19" s="272" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="270"/>
+      <c r="B19" s="272"/>
       <c r="C19" s="45"/>
       <c r="D19" s="45"/>
       <c r="E19" s="45"/>
       <c r="F19" s="60"/>
-      <c r="J19" s="271"/>
+      <c r="J19" s="273"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="270" t="s">
+      <c r="A20" s="272" t="s">
         <v>178</v>
       </c>
-      <c r="B20" s="270"/>
+      <c r="B20" s="272"/>
       <c r="C20" s="45"/>
       <c r="D20" s="45"/>
       <c r="E20" s="45"/>
       <c r="F20" s="30"/>
-      <c r="G20" s="272"/>
-      <c r="H20" s="272"/>
-      <c r="I20" s="272"/>
-      <c r="J20" s="272"/>
+      <c r="G20" s="274"/>
+      <c r="H20" s="274"/>
+      <c r="I20" s="274"/>
+      <c r="J20" s="274"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F21" s="30"/>
-      <c r="G21" s="273"/>
-      <c r="H21" s="274"/>
-      <c r="I21" s="274"/>
-      <c r="J21" s="275"/>
+      <c r="G21" s="275"/>
+      <c r="H21" s="276"/>
+      <c r="I21" s="276"/>
+      <c r="J21" s="277"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="259" t="s">
+      <c r="A22" s="261" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="259"/>
-      <c r="C22" s="276"/>
-      <c r="D22" s="276"/>
-      <c r="E22" s="276"/>
+      <c r="B22" s="261"/>
+      <c r="C22" s="278"/>
+      <c r="D22" s="278"/>
+      <c r="E22" s="278"/>
       <c r="F22" s="30"/>
-      <c r="G22" s="277"/>
-      <c r="H22" s="277"/>
-      <c r="I22" s="277"/>
-      <c r="J22" s="277"/>
+      <c r="G22" s="279"/>
+      <c r="H22" s="279"/>
+      <c r="I22" s="279"/>
+      <c r="J22" s="279"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="278" t="s">
+      <c r="A23" s="280" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="278"/>
+      <c r="B23" s="280"/>
       <c r="C23" s="45" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="45"/>
       <c r="E23" s="45"/>
       <c r="F23" s="30"/>
-      <c r="G23" s="277"/>
-      <c r="H23" s="277"/>
-      <c r="I23" s="277"/>
-      <c r="J23" s="277"/>
+      <c r="G23" s="279"/>
+      <c r="H23" s="279"/>
+      <c r="I23" s="279"/>
+      <c r="J23" s="279"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="279"/>
-      <c r="B24" s="279"/>
-      <c r="C24" s="280"/>
-      <c r="D24" s="280"/>
-      <c r="E24" s="280"/>
-      <c r="F24" s="281"/>
-      <c r="G24" s="277"/>
-      <c r="H24" s="277"/>
-      <c r="I24" s="277"/>
-      <c r="J24" s="277"/>
+      <c r="A24" s="281"/>
+      <c r="B24" s="281"/>
+      <c r="C24" s="282"/>
+      <c r="D24" s="282"/>
+      <c r="E24" s="282"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="279"/>
+      <c r="H24" s="279"/>
+      <c r="I24" s="279"/>
+      <c r="J24" s="279"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="33"/>
@@ -7080,28 +7089,28 @@
       <c r="E25" s="33"/>
       <c r="F25" s="30"/>
       <c r="G25" s="33"/>
-      <c r="H25" s="282"/>
-      <c r="I25" s="282"/>
-      <c r="J25" s="282"/>
-    </row>
-    <row r="26" s="283" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="283" t="s">
+      <c r="H25" s="284"/>
+      <c r="I25" s="284"/>
+      <c r="J25" s="284"/>
+    </row>
+    <row r="26" s="285" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="285" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="27" s="283" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="283" t="s">
+    <row r="27" s="285" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="285" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="28" s="283" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="283" t="s">
+    <row r="28" s="285" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="285" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="284"/>
-      <c r="B29" s="284"/>
+      <c r="A29" s="286"/>
+      <c r="B29" s="286"/>
       <c r="C29" s="30"/>
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
@@ -7110,7 +7119,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="30"/>
-      <c r="B30" s="284"/>
+      <c r="B30" s="286"/>
       <c r="C30" s="30"/>
       <c r="D30" s="30"/>
       <c r="E30" s="30"/>
@@ -7119,21 +7128,21 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="30"/>
-      <c r="B31" s="284"/>
-      <c r="C31" s="285"/>
-      <c r="D31" s="285"/>
-      <c r="E31" s="285"/>
-      <c r="F31" s="285"/>
-      <c r="G31" s="285"/>
+      <c r="B31" s="286"/>
+      <c r="C31" s="287"/>
+      <c r="D31" s="287"/>
+      <c r="E31" s="287"/>
+      <c r="F31" s="287"/>
+      <c r="G31" s="287"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="27"/>
-      <c r="B32" s="284"/>
-      <c r="C32" s="285"/>
-      <c r="D32" s="285"/>
-      <c r="E32" s="285"/>
-      <c r="F32" s="285"/>
-      <c r="G32" s="285"/>
+      <c r="B32" s="286"/>
+      <c r="C32" s="287"/>
+      <c r="D32" s="287"/>
+      <c r="E32" s="287"/>
+      <c r="F32" s="287"/>
+      <c r="G32" s="287"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12"/>

--- a/backend/public/templates/template_file.xlsx
+++ b/backend/public/templates/template_file.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Request Template" sheetId="1" state="visible" r:id="rId3"/>
@@ -2419,9 +2419,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1645560</xdr:colOff>
+      <xdr:colOff>1645200</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>169200</xdr:rowOff>
+      <xdr:rowOff>168840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2435,7 +2435,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1856880" cy="664560"/>
+          <a:ext cx="1856520" cy="664200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2462,9 +2462,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1578960</xdr:colOff>
+      <xdr:colOff>1578600</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>157320</xdr:rowOff>
+      <xdr:rowOff>156960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2478,7 +2478,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1860840" cy="664560"/>
+          <a:ext cx="1860480" cy="664200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2505,9 +2505,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>967680</xdr:colOff>
+      <xdr:colOff>967320</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>102600</xdr:rowOff>
+      <xdr:rowOff>102240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2521,7 +2521,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1360080" cy="483480"/>
+          <a:ext cx="1359720" cy="483120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2548,9 +2548,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1388160</xdr:colOff>
+      <xdr:colOff>1387800</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2564,7 +2564,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1951920" cy="506160"/>
+          <a:ext cx="1951560" cy="505800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
